--- a/multi-object-djsp/test_result/Rule/L9-1_metrics.xlsx
+++ b/multi-object-djsp/test_result/Rule/L9-1_metrics.xlsx
@@ -1,216 +1,180 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="10455" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20752" windowHeight="10455" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HV" sheetId="1" r:id="rId1"/>
-    <sheet name="CR" sheetId="2" r:id="rId2"/>
+    <sheet name="HV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hypervolume (HV)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Coverage" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="5">
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>RULE</t>
-  </si>
-  <si>
-    <t>DRL</t>
-  </si>
-  <si>
-    <t>L9-1</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -511,153 +475,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -711,11 +675,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1002,759 +1029,1399 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="12.7964601769912"/>
+    <col width="12.7964601769912" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>DRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="n">
+        <v>1.0029334245839</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.030301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C3" t="n">
+        <v>0.993643940883462</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.02762677596597</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="C4" t="n">
+        <v>0.997736106475729</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.03024196276084</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1.0029334245839</v>
-      </c>
-      <c r="D2">
-        <v>1.030301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0.993643940883462</v>
-      </c>
-      <c r="D3">
-        <v>1.02762677596597</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>0.997736106475729</v>
-      </c>
-      <c r="D4">
-        <v>1.03024196276084</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1.01227168825108</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1.02581727168668</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1.01727488381811</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>1.01940645549201</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1.02448109282821</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1.02728522264053</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>0.969549328643466</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.03013646741949</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1.00963594368827</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1.0294238011452</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1.01164220241003</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>1.00935955215126</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1.01652267924076</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>1.03027435138215</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1.00648538891669</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>1.02364860451289</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1.00111614563756</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>1.02994568826193</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>13</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1.0247159811815</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1.0226926782572</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>14</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>0.993074055838807</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1.03029577166769</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>15</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>0.972326202659465</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1.02842047591152</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>16</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>0.974798811548824</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>1.02995359863814</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>17</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1.00258454437236</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1.02994555490233</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>18</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1.01081597827354</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>1.03013810599698</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>19</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1.01749687180528</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>1.02848748888889</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>20</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1.00449091132537</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>1.02160078678038</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>21</v>
       </c>
-      <c r="C22">
-        <v>0.989677921180594</v>
-      </c>
-      <c r="D22">
+      <c r="C22" t="n">
+        <v>0.9896779211805939</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.0301729895978</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>22</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1.00304848897501</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1.03018537856345</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>23</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>0.963391525997757</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>1.02091523433955</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>24</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>0.99802209317909</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>1.03010786883197</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>25</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>1.0035233195316</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>1.0302837514363</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="12.7964601769912"/>
+    <col width="12.7964601769912" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>DRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D8" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D9" t="n">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
         <v>50</v>
       </c>
-      <c r="D3">
+      <c r="D12" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D15" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
         <v>50</v>
       </c>
-      <c r="D5">
+      <c r="D20" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
+      <c r="C21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>25</v>
       </c>
-      <c r="D7">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
+      <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>33.3333333333333</v>
-      </c>
-      <c r="D9">
-        <v>66.6666666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>12.5</v>
-      </c>
-      <c r="D10">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>50</v>
-      </c>
-      <c r="D12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>50</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>66.6666666666667</v>
-      </c>
-      <c r="D14">
-        <v>33.3333333333333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>20</v>
-      </c>
-      <c r="D16">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20">
-        <v>50</v>
-      </c>
-      <c r="D20">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-      <c r="C21">
-        <v>50</v>
-      </c>
-      <c r="D21">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24">
-        <v>33.3333333333333</v>
-      </c>
-      <c r="D24">
-        <v>66.6666666666667</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>DRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.026400780351806</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9485608516470435</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.000073145491536</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.030274091124067</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.006062594548288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.025963424913211</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9992267809206327</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.010373322296039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.011756166702928</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9986831059889905</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9804007944846653</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.030300215726268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9725103873096754</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.029693243992063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9881817976600008</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.030285003438802</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.025732484669174</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.029927327006404</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.00961191577979</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.024103474327604</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.025281323751031</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.030077715090576</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9712810848773867</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.030131266748072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.011199523902129</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.030286572929371</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9674489370061117</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.030019748264732</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>DRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.33333333333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>